--- a/数据表/Weapon.xlsx
+++ b/数据表/Weapon.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
   <si>
     <t>#</t>
   </si>
@@ -46,6 +46,15 @@
     <t>IconAssetName</t>
   </si>
   <si>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>PriceRandomPercent</t>
+  </si>
+  <si>
     <t>Attack</t>
   </si>
   <si>
@@ -70,6 +79,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>RarityType</t>
+  </si>
+  <si>
     <t>float</t>
   </si>
   <si>
@@ -91,6 +103,15 @@
     <t>图标资源名</t>
   </si>
   <si>
+    <t>道具品质</t>
+  </si>
+  <si>
+    <t>武器价格</t>
+  </si>
+  <si>
+    <t>价格浮动</t>
+  </si>
+  <si>
     <t>伤害</t>
   </si>
   <si>
@@ -116,6 +137,9 @@
   </si>
   <si>
     <t>Almighty_Icon</t>
+  </si>
+  <si>
+    <t>White</t>
   </si>
   <si>
     <t>[]</t>
@@ -737,7 +761,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -746,6 +770,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1058,21 +1085,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="5.81818181818182" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.4545454545455" style="1" customWidth="1"/>
     <col min="3" max="4" width="12" style="1" customWidth="1"/>
     <col min="5" max="5" width="18.8181818181818" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6363636363636" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.1818181818182" style="1" customWidth="1"/>
-    <col min="8" max="9" width="17.9090909090909" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5454545454545" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.8181818181818" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.3636363636364" customWidth="1"/>
+    <col min="7" max="7" width="19.9090909090909" customWidth="1"/>
+    <col min="8" max="8" width="26.9090909090909" customWidth="1"/>
+    <col min="9" max="9" width="10.6363636363636" style="1" customWidth="1"/>
+    <col min="10" max="10" width="18.1818181818182" style="1" customWidth="1"/>
+    <col min="11" max="12" width="17.9090909090909" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.5454545454545" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.8181818181818" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1086,8 +1116,11 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1113,141 +1146,186 @@
       <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>15</v>
+      <c r="J3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:14">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>201</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="2">
+        <v>35</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="3">
+        <v>120</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="I5" s="2">
         <v>100</v>
       </c>
-      <c r="G5" s="2">
+      <c r="J5" s="2">
         <v>1.5</v>
       </c>
-      <c r="H5" s="2">
+      <c r="K5" s="2">
         <v>3</v>
       </c>
-      <c r="I5" s="2">
+      <c r="L5" s="2">
         <v>10000</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>29</v>
+      <c r="M5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:14">
       <c r="B6" s="1">
         <v>202</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="1">
+        <v>35</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="3">
+        <v>130</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="I6" s="1">
         <v>120</v>
       </c>
-      <c r="G6" s="1">
+      <c r="J6" s="1">
         <v>1</v>
       </c>
-      <c r="H6" s="1">
+      <c r="K6" s="1">
         <v>10</v>
       </c>
-      <c r="I6" s="2">
+      <c r="L6" s="2">
         <v>10000</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>29</v>
+      <c r="M6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/数据表/Weapon.xlsx
+++ b/数据表/Weapon.xlsx
@@ -1094,9 +1094,9 @@
     <col min="5" max="5" width="18.8181818181818" style="1" customWidth="1"/>
     <col min="6" max="6" width="22.3636363636364" customWidth="1"/>
     <col min="7" max="7" width="19.9090909090909" customWidth="1"/>
-    <col min="8" max="8" width="26.9090909090909" customWidth="1"/>
+    <col min="8" max="8" width="22.5454545454545" customWidth="1"/>
     <col min="9" max="9" width="10.6363636363636" style="1" customWidth="1"/>
-    <col min="10" max="10" width="18.1818181818182" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15.0909090909091" style="1" customWidth="1"/>
     <col min="11" max="12" width="17.9090909090909" style="1" customWidth="1"/>
     <col min="13" max="13" width="13.5454545454545" style="1" customWidth="1"/>
     <col min="14" max="14" width="15.8181818181818" style="1" customWidth="1"/>
@@ -1278,7 +1278,7 @@
         <v>1.5</v>
       </c>
       <c r="K5" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L5" s="2">
         <v>10000</v>
@@ -1316,7 +1316,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L6" s="2">
         <v>10000</v>
